--- a/static/DolceFut-regrouped-sidebearings.xlsx
+++ b/static/DolceFut-regrouped-sidebearings.xlsx
@@ -450,28 +450,28 @@
         <v>A</v>
       </c>
       <c r="D2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="E2">
+        <v>-23</v>
+      </c>
+      <c r="F2">
         <v>-24</v>
       </c>
-      <c r="F2">
-        <v>-25</v>
-      </c>
       <c r="G2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="I2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="K2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="3">
@@ -488,25 +488,25 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="F3">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H3">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="J3">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="4">
@@ -526,22 +526,22 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G4">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H4">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I4">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J4">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K4">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="5">
@@ -561,22 +561,22 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="I5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="K5">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="6">
@@ -596,22 +596,22 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G6">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H6">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I6">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J6">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K6">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="7">
@@ -631,22 +631,22 @@
         <v>11</v>
       </c>
       <c r="F7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="I7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="K7">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="8">
@@ -666,22 +666,22 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G8">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H8">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I8">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J8">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K8">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="9">
@@ -701,22 +701,22 @@
         <v>11</v>
       </c>
       <c r="F9">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G9">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H9">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I9">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J9">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K9">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="10">
@@ -940,28 +940,28 @@
         <v>Delta</v>
       </c>
       <c r="D16">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="E16">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F16">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G16">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H16">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="I16">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J16">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="K16">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="17">
@@ -1340,13 +1340,13 @@
         <v>77</v>
       </c>
       <c r="I27">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="J27">
         <v>77</v>
       </c>
       <c r="K27">
-        <v>-26</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="28">
@@ -1372,16 +1372,16 @@
         <v>180</v>
       </c>
       <c r="H28">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="I28">
-        <v>-55</v>
+        <v>-54</v>
       </c>
       <c r="J28">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="K28">
-        <v>-55</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="29">
@@ -1407,16 +1407,16 @@
         <v>180</v>
       </c>
       <c r="H29">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="I29">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="J29">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="K29">
-        <v>-29</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="30">
@@ -1477,13 +1477,13 @@
         <v>150</v>
       </c>
       <c r="H31">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="I31">
         <v>75</v>
       </c>
       <c r="J31">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="K31">
         <v>75</v>
@@ -1512,16 +1512,16 @@
         <v>180</v>
       </c>
       <c r="H32">
-        <v>-45</v>
+        <v>-44</v>
       </c>
       <c r="I32">
-        <v>-66</v>
+        <v>-65</v>
       </c>
       <c r="J32">
-        <v>-45</v>
+        <v>-44</v>
       </c>
       <c r="K32">
-        <v>-66</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="33">
@@ -1573,25 +1573,25 @@
         <v>144</v>
       </c>
       <c r="E34">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="F34">
         <v>120</v>
       </c>
       <c r="G34">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H34">
         <v>120</v>
       </c>
       <c r="I34">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J34">
         <v>120</v>
       </c>
       <c r="K34">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="35">
@@ -1640,25 +1640,25 @@
         <v>L</v>
       </c>
       <c r="D36">
-        <v>-44</v>
+        <v>-43</v>
       </c>
       <c r="E36">
         <v>95</v>
       </c>
       <c r="F36">
-        <v>-74</v>
+        <v>-73</v>
       </c>
       <c r="G36">
         <v>71</v>
       </c>
       <c r="H36">
-        <v>-74</v>
+        <v>-73</v>
       </c>
       <c r="I36">
         <v>71</v>
       </c>
       <c r="J36">
-        <v>-74</v>
+        <v>-73</v>
       </c>
       <c r="K36">
         <v>71</v>
@@ -2063,25 +2063,25 @@
         <v>121</v>
       </c>
       <c r="E48">
+        <v>-20</v>
+      </c>
+      <c r="F48">
+        <v>120</v>
+      </c>
+      <c r="G48">
         <v>-21</v>
       </c>
-      <c r="F48">
-        <v>120</v>
-      </c>
-      <c r="G48">
-        <v>-22</v>
-      </c>
       <c r="H48">
         <v>120</v>
       </c>
       <c r="I48">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J48">
         <v>120</v>
       </c>
       <c r="K48">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="49">
@@ -2133,25 +2133,25 @@
         <v>144</v>
       </c>
       <c r="E50">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="F50">
         <v>120</v>
       </c>
       <c r="G50">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="H50">
         <v>120</v>
       </c>
       <c r="I50">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="J50">
         <v>120</v>
       </c>
       <c r="K50">
-        <v>-30</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="51">
@@ -2480,28 +2480,28 @@
         <v>V</v>
       </c>
       <c r="D60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="E60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="F60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="G60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="H60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="I60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="J60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="K60">
-        <v>-20</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="61">
@@ -2515,28 +2515,28 @@
         <v>W</v>
       </c>
       <c r="D61">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="E61">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F61">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="G61">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H61">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="I61">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J61">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="K61">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="62">
@@ -2550,28 +2550,28 @@
         <v>X</v>
       </c>
       <c r="D62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K62">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="63">
@@ -2690,25 +2690,25 @@
         <v>Z</v>
       </c>
       <c r="D66">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E66">
         <v>51</v>
       </c>
       <c r="F66">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G66">
         <v>50</v>
       </c>
       <c r="H66">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I66">
         <v>50</v>
       </c>
       <c r="J66">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -2731,19 +2731,19 @@
         <v>95</v>
       </c>
       <c r="F67">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G67">
         <v>51</v>
       </c>
       <c r="H67">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I67">
         <v>51</v>
       </c>
       <c r="J67">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K67">
         <v>51</v>
@@ -3626,13 +3626,13 @@
         <v>22</v>
       </c>
       <c r="I24">
-        <v>-55</v>
+        <v>-54</v>
       </c>
       <c r="J24">
         <v>22</v>
       </c>
       <c r="K24">
-        <v>-55</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="25">
@@ -3766,13 +3766,13 @@
         <v>87</v>
       </c>
       <c r="I28">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="J28">
         <v>87</v>
       </c>
       <c r="K28">
-        <v>-14</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="29">
@@ -3798,16 +3798,16 @@
         <v>168</v>
       </c>
       <c r="H29">
-        <v>-47</v>
+        <v>-46</v>
       </c>
       <c r="I29">
-        <v>-73</v>
+        <v>-72</v>
       </c>
       <c r="J29">
-        <v>-47</v>
+        <v>-46</v>
       </c>
       <c r="K29">
-        <v>-73</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="30">
@@ -3833,16 +3833,16 @@
         <v>168</v>
       </c>
       <c r="H30">
-        <v>-47</v>
+        <v>-46</v>
       </c>
       <c r="I30">
-        <v>-47</v>
+        <v>-46</v>
       </c>
       <c r="J30">
-        <v>-47</v>
+        <v>-46</v>
       </c>
       <c r="K30">
-        <v>-47</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="31">
@@ -3868,13 +3868,13 @@
         <v>168</v>
       </c>
       <c r="H31">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="I31">
         <v>87</v>
       </c>
       <c r="J31">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="K31">
         <v>87</v>
@@ -3996,28 +3996,28 @@
         <v>l</v>
       </c>
       <c r="D35">
-        <v>-65</v>
+        <v>-64</v>
       </c>
       <c r="E35">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="F35">
-        <v>-94</v>
+        <v>-93</v>
       </c>
       <c r="G35">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="H35">
-        <v>-94</v>
+        <v>-93</v>
       </c>
       <c r="I35">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="J35">
-        <v>-94</v>
+        <v>-93</v>
       </c>
       <c r="K35">
-        <v>-143</v>
+        <v>-142</v>
       </c>
     </row>
     <row r="36">
@@ -4066,25 +4066,25 @@
         <v>mu</v>
       </c>
       <c r="D37">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="E37">
         <v>77</v>
       </c>
       <c r="F37">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="G37">
         <v>77</v>
       </c>
       <c r="H37">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I37">
         <v>77</v>
       </c>
       <c r="J37">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="K37">
         <v>77</v>
@@ -4565,7 +4565,7 @@
         <v>120</v>
       </c>
       <c r="G51">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="H51">
         <v>120</v>
@@ -4979,25 +4979,25 @@
         <v>13</v>
       </c>
       <c r="E63">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="F63">
         <v>12</v>
       </c>
       <c r="G63">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="H63">
         <v>12</v>
       </c>
       <c r="I63">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J63">
         <v>12</v>
       </c>
       <c r="K63">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="64">
@@ -5020,19 +5020,19 @@
         <v>12</v>
       </c>
       <c r="G64">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="H64">
         <v>12</v>
       </c>
       <c r="I64">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J64">
         <v>12</v>
       </c>
       <c r="K64">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65">
@@ -5055,19 +5055,19 @@
         <v>12</v>
       </c>
       <c r="G65">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="H65">
         <v>12</v>
       </c>
       <c r="I65">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J65">
         <v>12</v>
       </c>
       <c r="K65">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="66">
@@ -6807,28 +6807,28 @@
         <v/>
       </c>
       <c r="D48">
-        <v>-362</v>
+        <v>-361</v>
       </c>
       <c r="E48">
-        <v>-240</v>
+        <v>-239</v>
       </c>
       <c r="F48">
-        <v>-362</v>
+        <v>-361</v>
       </c>
       <c r="G48">
-        <v>-240</v>
+        <v>-239</v>
       </c>
       <c r="H48">
-        <v>-362</v>
+        <v>-361</v>
       </c>
       <c r="I48">
-        <v>-240</v>
+        <v>-239</v>
       </c>
       <c r="J48">
-        <v>-362</v>
+        <v>-361</v>
       </c>
       <c r="K48">
-        <v>-240</v>
+        <v>-239</v>
       </c>
     </row>
     <row r="49">
@@ -9198,28 +9198,28 @@
         <v>A</v>
       </c>
       <c r="D2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="E2">
+        <v>-23</v>
+      </c>
+      <c r="F2">
         <v>-24</v>
       </c>
-      <c r="F2">
-        <v>-25</v>
-      </c>
       <c r="G2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="I2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="K2">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="3">
@@ -9236,25 +9236,25 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="F3">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="G3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H3">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="J3">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="K3">
-        <v>-104</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="4">
@@ -9621,25 +9621,25 @@
         <v>144</v>
       </c>
       <c r="E14">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="F14">
         <v>120</v>
       </c>
       <c r="G14">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="H14">
         <v>120</v>
       </c>
       <c r="I14">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="J14">
         <v>120</v>
       </c>
       <c r="K14">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="15">
@@ -9831,25 +9831,25 @@
         <v>121</v>
       </c>
       <c r="E20">
+        <v>-20</v>
+      </c>
+      <c r="F20">
+        <v>120</v>
+      </c>
+      <c r="G20">
         <v>-21</v>
       </c>
-      <c r="F20">
-        <v>120</v>
-      </c>
-      <c r="G20">
-        <v>-22</v>
-      </c>
       <c r="H20">
         <v>120</v>
       </c>
       <c r="I20">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J20">
         <v>120</v>
       </c>
       <c r="K20">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="21">
@@ -9901,25 +9901,25 @@
         <v>144</v>
       </c>
       <c r="E22">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="F22">
         <v>120</v>
       </c>
       <c r="G22">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="H22">
         <v>120</v>
       </c>
       <c r="I22">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="J22">
         <v>120</v>
       </c>
       <c r="K22">
-        <v>-30</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="23">
@@ -10038,28 +10038,28 @@
         <v>V</v>
       </c>
       <c r="D26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="E26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="F26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="G26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="H26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="I26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="J26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="K26">
-        <v>-20</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="27">
@@ -10073,28 +10073,28 @@
         <v>W</v>
       </c>
       <c r="D27">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="E27">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F27">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="G27">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H27">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="I27">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J27">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="K27">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="28">
@@ -10108,28 +10108,28 @@
         <v>X</v>
       </c>
       <c r="D28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K28">
-        <v>-10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="29">
@@ -10178,25 +10178,25 @@
         <v>Z</v>
       </c>
       <c r="D30">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E30">
         <v>51</v>
       </c>
       <c r="F30">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
       <c r="H30">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I30">
         <v>50</v>
       </c>
       <c r="J30">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -10519,13 +10519,13 @@
         <v>22</v>
       </c>
       <c r="I9">
-        <v>-55</v>
+        <v>-54</v>
       </c>
       <c r="J9">
         <v>22</v>
       </c>
       <c r="K9">
-        <v>-55</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="10">
@@ -10784,25 +10784,25 @@
         <v>mu</v>
       </c>
       <c r="D17">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="E17">
         <v>77</v>
       </c>
       <c r="F17">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="G17">
         <v>77</v>
       </c>
       <c r="H17">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I17">
         <v>77</v>
       </c>
       <c r="J17">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="K17">
         <v>77</v>
@@ -11038,7 +11038,7 @@
         <v>120</v>
       </c>
       <c r="G24">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="H24">
         <v>120</v>
@@ -11277,25 +11277,25 @@
         <v>13</v>
       </c>
       <c r="E31">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="F31">
         <v>12</v>
       </c>
       <c r="G31">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="H31">
         <v>12</v>
       </c>
       <c r="I31">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J31">
         <v>12</v>
       </c>
       <c r="K31">
-        <v>-12</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="32">
